--- a/artfynd/A 37896-2026 artfynd.xlsx
+++ b/artfynd/A 37896-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136715007</v>
       </c>
       <c r="B2" t="n">
-        <v>92692</v>
+        <v>92697</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37896-2026 artfynd.xlsx
+++ b/artfynd/A 37896-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136715007</v>
       </c>
       <c r="B2" t="n">
-        <v>92697</v>
+        <v>92699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37896-2026 artfynd.xlsx
+++ b/artfynd/A 37896-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136715007</v>
       </c>
       <c r="B2" t="n">
-        <v>92699</v>
+        <v>92701</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37896-2026 artfynd.xlsx
+++ b/artfynd/A 37896-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136715007</v>
       </c>
       <c r="B2" t="n">
-        <v>92701</v>
+        <v>92703</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37896-2026 artfynd.xlsx
+++ b/artfynd/A 37896-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136715007</v>
       </c>
       <c r="B2" t="n">
-        <v>92703</v>
+        <v>92704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37896-2026 artfynd.xlsx
+++ b/artfynd/A 37896-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136715007</v>
       </c>
       <c r="B2" t="n">
-        <v>92704</v>
+        <v>92710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37896-2026 artfynd.xlsx
+++ b/artfynd/A 37896-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136715007</v>
       </c>
       <c r="B2" t="n">
-        <v>92710</v>
+        <v>92714</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37896-2026 artfynd.xlsx
+++ b/artfynd/A 37896-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136715007</v>
       </c>
       <c r="B2" t="n">
-        <v>92714</v>
+        <v>92716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37896-2026 artfynd.xlsx
+++ b/artfynd/A 37896-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136715007</v>
       </c>
       <c r="B2" t="n">
-        <v>92716</v>
+        <v>92729</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37896-2026 artfynd.xlsx
+++ b/artfynd/A 37896-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136715007</v>
       </c>
       <c r="B2" t="n">
-        <v>92729</v>
+        <v>92731</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37896-2026 artfynd.xlsx
+++ b/artfynd/A 37896-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136715007</v>
       </c>
       <c r="B2" t="n">
-        <v>92731</v>
+        <v>92734</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37896-2026 artfynd.xlsx
+++ b/artfynd/A 37896-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136715007</v>
       </c>
       <c r="B2" t="n">
-        <v>92734</v>
+        <v>92744</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
